--- a/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
@@ -57,6 +57,9 @@
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
@@ -75,16 +78,13 @@
     <t xml:space="preserve">La Higuera</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -520,7 +520,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>179.61</v>
+        <v>198.01</v>
       </c>
     </row>
     <row r="3">
@@ -537,7 +537,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>174.3</v>
+        <v>189.72</v>
       </c>
     </row>
     <row r="4">
@@ -554,7 +554,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>164.56</v>
+        <v>177.54</v>
       </c>
     </row>
     <row r="5">
@@ -571,7 +571,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>124.49</v>
+        <v>134.93</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>120.95</v>
+        <v>130.31</v>
       </c>
     </row>
     <row r="7">
@@ -605,7 +605,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>118.91</v>
+        <v>127.69</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>113.77</v>
+        <v>122.34</v>
       </c>
     </row>
     <row r="9">
@@ -633,13 +633,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4303</v>
+        <v>4105</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>112.35</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="10">
@@ -650,13 +650,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4204</v>
+        <v>4303</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>111.47</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="11">
@@ -667,13 +667,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4103</v>
+        <v>4204</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>110.42</v>
+        <v>119.61</v>
       </c>
     </row>
     <row r="12">
@@ -684,13 +684,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4301</v>
+        <v>4103</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>103.95</v>
+        <v>117.95</v>
       </c>
     </row>
     <row r="13">
@@ -701,13 +701,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4101</v>
+        <v>4301</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>97.63</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="14">
@@ -715,16 +715,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>93.02</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="15">
@@ -732,16 +732,16 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>90.18</v>
+        <v>99.69</v>
       </c>
     </row>
     <row r="16">
@@ -752,10 +752,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4104</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>98.59</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:25</t>
+    <t xml:space="preserve">2026-10-04 10:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:42</t>
+    <t xml:space="preserve">2026-10-05 16:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
